--- a/sample_files/LABPAY_1-10_sample_files/cbs_costitems_v1.xlsx
+++ b/sample_files/LABPAY_1-10_sample_files/cbs_costitems_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\construction-erp\sample_files\LABPAY_1-10_sample_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{971BF051-91CA-4B0E-AE1A-9BCEF126B03F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E635B85-07E7-42BF-B736-3820389D2C3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C35DAF8F-D969-43F0-81C8-EE18DEB2DC23}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C35DAF8F-D969-43F0-81C8-EE18DEB2DC23}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
